--- a/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-oral.xlsx
@@ -36,26 +36,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">用 45–90 秒解释 grouped ordering 为何可能加速，以及何时不能从 benchmark 宣布胜负。</t>
+          <t xml:space="preserve">口述 grouped ordering 的收益与证据边界。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：grouped ordering 通过缩短相邻 program 的 A/B tile 复用距离提高 L2 locality，但收益依赖工作集、配置和架构。
-• [T#B#机制]：把执行窗口从狭长条带改成更紧凑的二维区域，减少需要同时触及的输入 tile。
-• [T#B#适用条件]：二维 grid 足够大、复用数据能驻留 L2、kernel 对内存流量敏感，且 group size 匹配配置。
-• [T#B#证据判断]：若 AB/BA 方向相反且同一配置自身漂移更大，只能判为当前方法证据不足。
-[T#B,!c47f17#边界]：单一设备、shape 和 group 1/2 的结果不能泛化为所有配置或架构。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：grouped ordering 通过改善相邻 program 的输入 tile 复用争取性能，是否有效需要受控证据。
+• [T#B#复用机会]：重排 program 对 tile 的访问，使可复用 A/B 数据的访问间隔有机会缩短。
+• [T#B#机制]：若复用距离缩短到 L2 驻留窗口内，可减少重复数据访问；二维网格、访存瓶颈和分组配置都会影响收益。
+• [T#B#判断]：若配置差异与运行漂移无法稳定分离，就报告证据不足，既不宣布胜负也不声称真实影响很小。
+[T#B,!c47f17#边界]：单台设备和单个 shape 的比较，只支持相同测量范围内的结论。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">L2 复用距离；二维 tile grid；配置与架构边界；证据不足不等于影响很小</t>
+          <t xml:space="preserve">输入 tile 复用机会；L2 驻留与复用距离；配置和架构条件；证据不足及外推边界</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 03 学习记录 · 性能综合</t>
+          <t xml:space="preserve">Lesson 03 · 8/17 概念记录；8/19 性能解释</t>
         </is>
       </c>
     </row>

--- a/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-oral.xlsx
@@ -36,21 +36,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">口述 grouped ordering 的收益与证据边界。</t>
+          <t xml:space="preserve">请用 45–90 秒解释：分块矩阵乘法的 grouped ordering 如何争取 L2 复用收益；如果两种分组配置的 benchmark 差异与运行漂移混在一起，又应该如何报告结论？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：grouped ordering 通过改善相邻 program 的输入 tile 复用争取性能，是否有效需要受控证据。
-• [T#B#复用机会]：重排 program 对 tile 的访问，使可复用 A/B 数据的访问间隔有机会缩短。
-• [T#B#机制]：若复用距离缩短到 L2 驻留窗口内，可减少重复数据访问；二维网格、访存瓶颈和分组配置都会影响收益。
-• [T#B#判断]：若配置差异与运行漂移无法稳定分离，就报告证据不足，既不宣布胜负也不声称真实影响很小。
-[T#B,!c47f17#边界]：单台设备和单个 shape 的比较，只支持相同测量范围内的结论。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：Grouped ordering 尝试改善输入 tile 的访问局部性，但是否加速必须由目标设备上的可区分测量支持。
+• [T#B#复用机制]：重排 PID 到输出 tile 的映射，让需要相同 A/B tile 的 program 在映射上更接近。若重复访问发生在数据仍驻留 L2 的时间窗口内，就有机会减少显存读取。
+• [T#B#生效条件]：二维 tile 网格要有足够重排空间，计算也要对访存足够敏感；分组大小、block 配置、并发窗口和架构都会影响复用是否兑现。
+• [T#B#如何解释测量]：若多轮测试仍无法把配置影响与运行状态漂移稳定分离，应报告当前证据不足。不能宣布哪组更快，也不能进一步证明真实效应很小。
+[T#B,!c47f17#边界]：这些判断仅适用于所测的设备、shape、launch 配置与计时口径；一次对照不能支持跨设备、跨形状或所有分组大小的性能结论。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">输入 tile 复用机会；L2 驻留与复用距离；配置和架构条件；证据不足及外推边界</t>
+          <t xml:space="preserve">说明 A/B tile 的复用机会来自哪些输出块；说明复用间隔必须落在 L2 驻留窗口内；说明设备、形状和分组配置的影响；把无法区分表述为证据不足，并限制外推范围</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-oral.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -36,21 +36,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">请用 45–90 秒解释：分块矩阵乘法的 grouped ordering 如何争取 L2 复用收益；如果两种分组配置的 benchmark 差异与运行漂移混在一起，又应该如何报告结论？</t>
+          <t xml:space="preserve">面试官问：“你在 RTX 5090 上只改 GROUP_SIZE_M=1/2 对比 matmul，看不出稳定的性能差异，那 grouped ordering 还有用吗？”请在 60–90 秒内回答：它靠什么机制争取收益、什么条件下更可能见效，以及你会怎样解读这次结果。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：Grouped ordering 尝试改善输入 tile 的访问局部性，但是否加速必须由目标设备上的可区分测量支持。
-• [T#B#复用机制]：重排 PID 到输出 tile 的映射，让需要相同 A/B tile 的 program 在映射上更接近。若重复访问发生在数据仍驻留 L2 的时间窗口内，就有机会减少显存读取。
-• [T#B#生效条件]：二维 tile 网格要有足够重排空间，计算也要对访存足够敏感；分组大小、block 配置、并发窗口和架构都会影响复用是否兑现。
-• [T#B#如何解释测量]：若多轮测试仍无法把配置影响与运行状态漂移稳定分离，应报告当前证据不足。不能宣布哪组更快，也不能进一步证明真实效应很小。
-[T#B,!c47f17#边界]：这些判断仅适用于所测的设备、shape、launch 配置与计时口径；一次对照不能支持跨设备、跨形状或所有分组大小的性能结论。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：有用，但不是必然加速：它靠缩短 A/B tile 的复用间隔来争取 L2 命中；这次对照只说明在本机该配置下，差异无法与运行漂移区分，不能说明它没用。
+• [T#B#复用机制]：同一输出 tile 列的 program 在相同 K 段共用 B tile，同一 tile 行的共用 A tile；分组让这些 program 在映射上更接近，若再次访问时数据仍在 L2，就能少读显存。
+• [T#B#生效条件]：二维 tile 网格较大、kernel 对访存敏感、group size 与并发窗口和 block 配置匹配时更可能见效；PID 映射也不强制实际调度顺序。
+• [T#B#解读结果]：两种配置的差异与约 4% 的运行漂移混在一起，只能报告证据不足：既不能说哪组更快，也不能说真实影响很小；结论只限所测设备、shape、配置和计时口径。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明 A/B tile 的复用机会来自哪些输出块；说明复用间隔必须落在 L2 驻留窗口内；说明设备、形状和分组配置的影响；把无法区分表述为证据不足，并限制外推范围</t>
+          <t xml:space="preserve">说出复用来源：同列 program 共用 B tile、同行共用 A tile，分组让它们在映射上更接近；说明复用必须发生在数据仍驻留 L2 时，才会减少显存读取；说出至少两个生效条件：二维 tile 网格较大、访存敏感、group size 与并发窗口匹配；把这次结果表述为无法与漂移区分的证据不足，不说成影响很小，并限定外推范围</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -59,6 +58,32 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">面试官请你走读 Triton 官方 matmul 教程的 kernel：C\[M,N\]=A\[M,K\]×B\[K,N\]，每个 program 负责一个 \[BLOCK_M,BLOCK_N\] 的输出 tile。请在 60–90 秒内按执行顺序讲清：program 怎样从 pid 找到自己的 tile、怎样沿 K 算完它，以及 M/N/K 三类边界分别在哪一步处理、为什么。</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：pid 先映射到输出 tile，再沿 K 循环乘加到 FP32 accumulator，最后带 mask 写回；K 尾部在 load 时补零，M/N 越界只在写回时丢弃。
+• [T#B#定位 tile]：grouped ordering 把线性 pid 映射成 (pid_m, pid_n)：组内行号 p%h、列号 p//h；尾组的 h 取实际剩余行数，否则会越界又漏块。
+• [T#B#K 循环]：accumulator 为 \[BLOCK_M,BLOCK_N\]、初值为零；每轮加载 A 的 \[BLOCK_M,BLOCK_K\] 与 B 的 \[BLOCK_K,BLOCK_N\]，乘加后两边读取位置沿 K 前进 BLOCK_K。
+• [T#B#K 尾部]：K 是归约轴：越界的 K 位置必须在 load 时补零，错误项一旦加进有效的 C\[i,j\]，写回 mask 就剔除不了。
+• [T#B#M/N 边界]：M/N 是独立的输出坐标：越界行列可取模读合法的替代数据，结果在写回时按原始行列号 mask 丢弃；直接用 load mask 也正确，取模不保证更快。</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pid 经分组映射到输出 tile，尾组用实际组高，避免越界和漏块；FP32 accumulator 固定在一个输出 tile 上，沿 K 逐段加载 A、B 并乘加，读取位置沿 K 前进；K 尾部在 load 时补零，因为累加进有效输出的错误项无法被写回 mask 剔除；M/N 越界可取模读替代数据，写回时按原始行列号 mask 丢弃</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesson 03 · 8/17 概念记录；8/19 实践记录</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>